--- a/artfynd/A 32223-2024 artfynd.xlsx
+++ b/artfynd/A 32223-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119719060</v>
+        <v>119719049</v>
       </c>
       <c r="B3" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>701264</v>
+        <v>701148</v>
       </c>
       <c r="R3" t="n">
-        <v>7155153</v>
+        <v>7155258</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119719049</v>
+        <v>119719060</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>701148</v>
+        <v>701264</v>
       </c>
       <c r="R4" t="n">
-        <v>7155258</v>
+        <v>7155153</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 32223-2024 artfynd.xlsx
+++ b/artfynd/A 32223-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119719051</v>
+        <v>119719038</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>701248</v>
+        <v>701148</v>
       </c>
       <c r="R2" t="n">
-        <v>7155175</v>
+        <v>7155247</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119719049</v>
+        <v>119719051</v>
       </c>
       <c r="B3" t="n">
         <v>91840</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>701148</v>
+        <v>701248</v>
       </c>
       <c r="R3" t="n">
-        <v>7155258</v>
+        <v>7155175</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119719060</v>
+        <v>119719059</v>
       </c>
       <c r="B4" t="n">
         <v>91834</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>701264</v>
+        <v>701141</v>
       </c>
       <c r="R4" t="n">
-        <v>7155153</v>
+        <v>7155241</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119719035</v>
+        <v>119719053</v>
       </c>
       <c r="B5" t="n">
-        <v>91844</v>
+        <v>91840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>701521</v>
+        <v>701434</v>
       </c>
       <c r="R5" t="n">
-        <v>7154839</v>
+        <v>7155013</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119719030</v>
+        <v>119719035</v>
       </c>
       <c r="B6" t="n">
-        <v>90527</v>
+        <v>91844</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>4365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>701166</v>
+        <v>701521</v>
       </c>
       <c r="R6" t="n">
-        <v>7155254</v>
+        <v>7154839</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119719059</v>
+        <v>119719052</v>
       </c>
       <c r="B7" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>701141</v>
+        <v>701306</v>
       </c>
       <c r="R7" t="n">
-        <v>7155241</v>
+        <v>7155111</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119719040</v>
+        <v>119719033</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
+        <v>91883</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>5448</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>701361</v>
+        <v>701520</v>
       </c>
       <c r="R8" t="n">
-        <v>7155081</v>
+        <v>7154839</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119719050</v>
+        <v>119719048</v>
       </c>
       <c r="B9" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701225</v>
+        <v>701693</v>
       </c>
       <c r="R9" t="n">
-        <v>7155202</v>
+        <v>7154711</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119719033</v>
+        <v>119719050</v>
       </c>
       <c r="B10" t="n">
-        <v>91883</v>
+        <v>91840</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701520</v>
+        <v>701225</v>
       </c>
       <c r="R10" t="n">
-        <v>7154839</v>
+        <v>7155202</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119719055</v>
+        <v>119719030</v>
       </c>
       <c r="B11" t="n">
-        <v>91840</v>
+        <v>90527</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701650</v>
+        <v>701166</v>
       </c>
       <c r="R11" t="n">
-        <v>7154795</v>
+        <v>7155254</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119719054</v>
+        <v>119719060</v>
       </c>
       <c r="B12" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701492</v>
+        <v>701264</v>
       </c>
       <c r="R12" t="n">
-        <v>7154832</v>
+        <v>7155153</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119719042</v>
+        <v>119719055</v>
       </c>
       <c r="B13" t="n">
-        <v>96868</v>
+        <v>91840</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>701561</v>
+        <v>701650</v>
       </c>
       <c r="R13" t="n">
-        <v>7154811</v>
+        <v>7154795</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119719053</v>
+        <v>119719049</v>
       </c>
       <c r="B14" t="n">
         <v>91840</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>701434</v>
+        <v>701148</v>
       </c>
       <c r="R14" t="n">
-        <v>7155013</v>
+        <v>7155258</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119719038</v>
+        <v>119719054</v>
       </c>
       <c r="B15" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>701148</v>
+        <v>701492</v>
       </c>
       <c r="R15" t="n">
-        <v>7155247</v>
+        <v>7154832</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119719052</v>
+        <v>119719042</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
+        <v>96868</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>701306</v>
+        <v>701561</v>
       </c>
       <c r="R16" t="n">
-        <v>7155111</v>
+        <v>7154811</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119719048</v>
+        <v>119719040</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>91852</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>701693</v>
+        <v>701361</v>
       </c>
       <c r="R17" t="n">
-        <v>7154711</v>
+        <v>7155081</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 32223-2024 artfynd.xlsx
+++ b/artfynd/A 32223-2024 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119719048</v>
+        <v>119719050</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701693</v>
+        <v>701225</v>
       </c>
       <c r="R9" t="n">
-        <v>7154711</v>
+        <v>7155202</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119719050</v>
+        <v>119719048</v>
       </c>
       <c r="B10" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701225</v>
+        <v>701693</v>
       </c>
       <c r="R10" t="n">
-        <v>7155202</v>
+        <v>7154711</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 32223-2024 artfynd.xlsx
+++ b/artfynd/A 32223-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119719038</v>
+        <v>119719060</v>
       </c>
       <c r="B2" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>701148</v>
+        <v>701264</v>
       </c>
       <c r="R2" t="n">
-        <v>7155247</v>
+        <v>7155153</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119719051</v>
+        <v>119719038</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>701248</v>
+        <v>701148</v>
       </c>
       <c r="R3" t="n">
-        <v>7155175</v>
+        <v>7155247</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119719059</v>
+        <v>119719033</v>
       </c>
       <c r="B4" t="n">
-        <v>91834</v>
+        <v>91883</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>5448</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>701141</v>
+        <v>701520</v>
       </c>
       <c r="R4" t="n">
-        <v>7155241</v>
+        <v>7154839</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119719053</v>
+        <v>119719040</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>701434</v>
+        <v>701361</v>
       </c>
       <c r="R5" t="n">
-        <v>7155013</v>
+        <v>7155081</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119719035</v>
+        <v>119719059</v>
       </c>
       <c r="B6" t="n">
-        <v>91844</v>
+        <v>91834</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>701521</v>
+        <v>701141</v>
       </c>
       <c r="R6" t="n">
-        <v>7154839</v>
+        <v>7155241</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119719052</v>
+        <v>119719054</v>
       </c>
       <c r="B7" t="n">
         <v>91840</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>701306</v>
+        <v>701492</v>
       </c>
       <c r="R7" t="n">
-        <v>7155111</v>
+        <v>7154832</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119719033</v>
+        <v>119719049</v>
       </c>
       <c r="B8" t="n">
-        <v>91883</v>
+        <v>91840</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>701520</v>
+        <v>701148</v>
       </c>
       <c r="R8" t="n">
-        <v>7154839</v>
+        <v>7155258</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119719050</v>
+        <v>119719042</v>
       </c>
       <c r="B9" t="n">
-        <v>91840</v>
+        <v>96868</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701225</v>
+        <v>701561</v>
       </c>
       <c r="R9" t="n">
-        <v>7155202</v>
+        <v>7154811</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119719048</v>
+        <v>119719030</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>90527</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701693</v>
+        <v>701166</v>
       </c>
       <c r="R10" t="n">
-        <v>7154711</v>
+        <v>7155254</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119719030</v>
+        <v>119719058</v>
       </c>
       <c r="B11" t="n">
-        <v>90527</v>
+        <v>91834</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701166</v>
+        <v>701147</v>
       </c>
       <c r="R11" t="n">
-        <v>7155254</v>
+        <v>7155226</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119719060</v>
+        <v>119719050</v>
       </c>
       <c r="B12" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701264</v>
+        <v>701225</v>
       </c>
       <c r="R12" t="n">
-        <v>7155153</v>
+        <v>7155202</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119719055</v>
+        <v>119719051</v>
       </c>
       <c r="B13" t="n">
         <v>91840</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>701650</v>
+        <v>701248</v>
       </c>
       <c r="R13" t="n">
-        <v>7154795</v>
+        <v>7155175</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119719049</v>
+        <v>119719053</v>
       </c>
       <c r="B14" t="n">
         <v>91840</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>701148</v>
+        <v>701434</v>
       </c>
       <c r="R14" t="n">
-        <v>7155258</v>
+        <v>7155013</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119719054</v>
+        <v>119719055</v>
       </c>
       <c r="B15" t="n">
         <v>91840</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>701492</v>
+        <v>701650</v>
       </c>
       <c r="R15" t="n">
-        <v>7154832</v>
+        <v>7154795</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119719042</v>
+        <v>119719052</v>
       </c>
       <c r="B16" t="n">
-        <v>96868</v>
+        <v>91840</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>701561</v>
+        <v>701306</v>
       </c>
       <c r="R16" t="n">
-        <v>7154811</v>
+        <v>7155111</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119719040</v>
+        <v>119719048</v>
       </c>
       <c r="B17" t="n">
-        <v>91852</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>701361</v>
+        <v>701693</v>
       </c>
       <c r="R17" t="n">
-        <v>7155081</v>
+        <v>7154711</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119719058</v>
+        <v>119719035</v>
       </c>
       <c r="B18" t="n">
-        <v>91834</v>
+        <v>91844</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,25 +2319,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>701147</v>
+        <v>701521</v>
       </c>
       <c r="R18" t="n">
-        <v>7155226</v>
+        <v>7154839</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 32223-2024 artfynd.xlsx
+++ b/artfynd/A 32223-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119719060</v>
+        <v>119719050</v>
       </c>
       <c r="B2" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>701264</v>
+        <v>701225</v>
       </c>
       <c r="R2" t="n">
-        <v>7155153</v>
+        <v>7155202</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119719038</v>
+        <v>119719053</v>
       </c>
       <c r="B3" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>701148</v>
+        <v>701434</v>
       </c>
       <c r="R3" t="n">
-        <v>7155247</v>
+        <v>7155013</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119719040</v>
+        <v>119719042</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
+        <v>96868</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>701361</v>
+        <v>701561</v>
       </c>
       <c r="R5" t="n">
-        <v>7155081</v>
+        <v>7154811</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119719059</v>
+        <v>119719051</v>
       </c>
       <c r="B6" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>701141</v>
+        <v>701248</v>
       </c>
       <c r="R6" t="n">
-        <v>7155241</v>
+        <v>7155175</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119719054</v>
+        <v>119719058</v>
       </c>
       <c r="B7" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>701492</v>
+        <v>701147</v>
       </c>
       <c r="R7" t="n">
-        <v>7154832</v>
+        <v>7155226</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119719042</v>
+        <v>119719035</v>
       </c>
       <c r="B9" t="n">
-        <v>96868</v>
+        <v>91844</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>4365</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701561</v>
+        <v>701521</v>
       </c>
       <c r="R9" t="n">
-        <v>7154811</v>
+        <v>7154839</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119719030</v>
+        <v>119719052</v>
       </c>
       <c r="B10" t="n">
-        <v>90527</v>
+        <v>91840</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701166</v>
+        <v>701306</v>
       </c>
       <c r="R10" t="n">
-        <v>7155254</v>
+        <v>7155111</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119719058</v>
+        <v>119719060</v>
       </c>
       <c r="B11" t="n">
         <v>91834</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701147</v>
+        <v>701264</v>
       </c>
       <c r="R11" t="n">
-        <v>7155226</v>
+        <v>7155153</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119719050</v>
+        <v>119719030</v>
       </c>
       <c r="B12" t="n">
-        <v>91840</v>
+        <v>90527</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701225</v>
+        <v>701166</v>
       </c>
       <c r="R12" t="n">
-        <v>7155202</v>
+        <v>7155254</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119719051</v>
+        <v>119719040</v>
       </c>
       <c r="B13" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>701248</v>
+        <v>701361</v>
       </c>
       <c r="R13" t="n">
-        <v>7155175</v>
+        <v>7155081</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119719053</v>
+        <v>119719055</v>
       </c>
       <c r="B14" t="n">
         <v>91840</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>701434</v>
+        <v>701650</v>
       </c>
       <c r="R14" t="n">
-        <v>7155013</v>
+        <v>7154795</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119719055</v>
+        <v>119719048</v>
       </c>
       <c r="B15" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>701650</v>
+        <v>701693</v>
       </c>
       <c r="R15" t="n">
-        <v>7154795</v>
+        <v>7154711</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119719052</v>
+        <v>119719038</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>701306</v>
+        <v>701148</v>
       </c>
       <c r="R16" t="n">
-        <v>7155111</v>
+        <v>7155247</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119719048</v>
+        <v>119719054</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>701693</v>
+        <v>701492</v>
       </c>
       <c r="R17" t="n">
-        <v>7154711</v>
+        <v>7154832</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119719035</v>
+        <v>119719059</v>
       </c>
       <c r="B18" t="n">
-        <v>91844</v>
+        <v>91834</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,25 +2319,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>701521</v>
+        <v>701141</v>
       </c>
       <c r="R18" t="n">
-        <v>7154839</v>
+        <v>7155241</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 32223-2024 artfynd.xlsx
+++ b/artfynd/A 32223-2024 artfynd.xlsx
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119719038</v>
+        <v>119719054</v>
       </c>
       <c r="B16" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>701148</v>
+        <v>701492</v>
       </c>
       <c r="R16" t="n">
-        <v>7155247</v>
+        <v>7154832</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119719054</v>
+        <v>119719038</v>
       </c>
       <c r="B17" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>701492</v>
+        <v>701148</v>
       </c>
       <c r="R17" t="n">
-        <v>7154832</v>
+        <v>7155247</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 32223-2024 artfynd.xlsx
+++ b/artfynd/A 32223-2024 artfynd.xlsx
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119719030</v>
+        <v>119719040</v>
       </c>
       <c r="B12" t="n">
-        <v>90527</v>
+        <v>91852</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701166</v>
+        <v>701361</v>
       </c>
       <c r="R12" t="n">
-        <v>7155254</v>
+        <v>7155081</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119719040</v>
+        <v>119719030</v>
       </c>
       <c r="B13" t="n">
-        <v>91852</v>
+        <v>90527</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>701361</v>
+        <v>701166</v>
       </c>
       <c r="R13" t="n">
-        <v>7155081</v>
+        <v>7155254</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119719054</v>
+        <v>119719038</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>701492</v>
+        <v>701148</v>
       </c>
       <c r="R16" t="n">
-        <v>7154832</v>
+        <v>7155247</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119719038</v>
+        <v>119719054</v>
       </c>
       <c r="B17" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>701148</v>
+        <v>701492</v>
       </c>
       <c r="R17" t="n">
-        <v>7155247</v>
+        <v>7154832</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 32223-2024 artfynd.xlsx
+++ b/artfynd/A 32223-2024 artfynd.xlsx
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119719040</v>
+        <v>119719030</v>
       </c>
       <c r="B12" t="n">
-        <v>91852</v>
+        <v>90527</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701361</v>
+        <v>701166</v>
       </c>
       <c r="R12" t="n">
-        <v>7155081</v>
+        <v>7155254</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119719030</v>
+        <v>119719040</v>
       </c>
       <c r="B13" t="n">
-        <v>90527</v>
+        <v>91852</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>701166</v>
+        <v>701361</v>
       </c>
       <c r="R13" t="n">
-        <v>7155254</v>
+        <v>7155081</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 32223-2024 artfynd.xlsx
+++ b/artfynd/A 32223-2024 artfynd.xlsx
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119719030</v>
+        <v>119719040</v>
       </c>
       <c r="B12" t="n">
-        <v>90527</v>
+        <v>91852</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701166</v>
+        <v>701361</v>
       </c>
       <c r="R12" t="n">
-        <v>7155254</v>
+        <v>7155081</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119719040</v>
+        <v>119719030</v>
       </c>
       <c r="B13" t="n">
-        <v>91852</v>
+        <v>90527</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>701361</v>
+        <v>701166</v>
       </c>
       <c r="R13" t="n">
-        <v>7155081</v>
+        <v>7155254</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 32223-2024 artfynd.xlsx
+++ b/artfynd/A 32223-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119719050</v>
+        <v>119719033</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
+        <v>91901</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>701225</v>
+        <v>701520</v>
       </c>
       <c r="R2" t="n">
-        <v>7155202</v>
+        <v>7154839</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119719053</v>
+        <v>119719051</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>701434</v>
+        <v>701248</v>
       </c>
       <c r="R3" t="n">
-        <v>7155013</v>
+        <v>7155175</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119719033</v>
+        <v>119719060</v>
       </c>
       <c r="B4" t="n">
-        <v>91883</v>
+        <v>91852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>701520</v>
+        <v>701264</v>
       </c>
       <c r="R4" t="n">
-        <v>7154839</v>
+        <v>7155153</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119719042</v>
+        <v>119719050</v>
       </c>
       <c r="B5" t="n">
-        <v>96868</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>701561</v>
+        <v>701225</v>
       </c>
       <c r="R5" t="n">
-        <v>7154811</v>
+        <v>7155202</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119719051</v>
+        <v>119719055</v>
       </c>
       <c r="B6" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>701248</v>
+        <v>701650</v>
       </c>
       <c r="R6" t="n">
-        <v>7155175</v>
+        <v>7154795</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119719058</v>
+        <v>119719040</v>
       </c>
       <c r="B7" t="n">
-        <v>91834</v>
+        <v>91870</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>701147</v>
+        <v>701361</v>
       </c>
       <c r="R7" t="n">
-        <v>7155226</v>
+        <v>7155081</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119719049</v>
+        <v>119719038</v>
       </c>
       <c r="B8" t="n">
-        <v>91840</v>
+        <v>91874</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1330,7 +1330,7 @@
         <v>701148</v>
       </c>
       <c r="R8" t="n">
-        <v>7155258</v>
+        <v>7155247</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119719035</v>
+        <v>119719059</v>
       </c>
       <c r="B9" t="n">
-        <v>91844</v>
+        <v>91852</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701521</v>
+        <v>701141</v>
       </c>
       <c r="R9" t="n">
-        <v>7154839</v>
+        <v>7155241</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119719052</v>
+        <v>119719048</v>
       </c>
       <c r="B10" t="n">
-        <v>91840</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701306</v>
+        <v>701693</v>
       </c>
       <c r="R10" t="n">
-        <v>7155111</v>
+        <v>7154711</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119719060</v>
+        <v>119719054</v>
       </c>
       <c r="B11" t="n">
-        <v>91834</v>
+        <v>91858</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701264</v>
+        <v>701492</v>
       </c>
       <c r="R11" t="n">
-        <v>7155153</v>
+        <v>7154832</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119719030</v>
+        <v>119719052</v>
       </c>
       <c r="B12" t="n">
-        <v>90527</v>
+        <v>91858</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701166</v>
+        <v>701306</v>
       </c>
       <c r="R12" t="n">
-        <v>7155254</v>
+        <v>7155111</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119719040</v>
+        <v>119719035</v>
       </c>
       <c r="B13" t="n">
-        <v>91852</v>
+        <v>91862</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>701361</v>
+        <v>701521</v>
       </c>
       <c r="R13" t="n">
-        <v>7155081</v>
+        <v>7154839</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119719055</v>
+        <v>119719058</v>
       </c>
       <c r="B14" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>701650</v>
+        <v>701147</v>
       </c>
       <c r="R14" t="n">
-        <v>7154795</v>
+        <v>7155226</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119719048</v>
+        <v>119719049</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>91858</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>701693</v>
+        <v>701148</v>
       </c>
       <c r="R15" t="n">
-        <v>7154711</v>
+        <v>7155258</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119719038</v>
+        <v>119719042</v>
       </c>
       <c r="B16" t="n">
-        <v>91856</v>
+        <v>96891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2059</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>701148</v>
+        <v>701561</v>
       </c>
       <c r="R16" t="n">
-        <v>7155247</v>
+        <v>7154811</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119719054</v>
+        <v>119719030</v>
       </c>
       <c r="B17" t="n">
-        <v>91840</v>
+        <v>90545</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>701492</v>
+        <v>701166</v>
       </c>
       <c r="R17" t="n">
-        <v>7154832</v>
+        <v>7155254</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119719059</v>
+        <v>119719053</v>
       </c>
       <c r="B18" t="n">
-        <v>91834</v>
+        <v>91858</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,25 +2319,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>701141</v>
+        <v>701434</v>
       </c>
       <c r="R18" t="n">
-        <v>7155241</v>
+        <v>7155013</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 32223-2024 artfynd.xlsx
+++ b/artfynd/A 32223-2024 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119719033</v>
+        <v>119719038</v>
       </c>
       <c r="B2" t="n">
-        <v>91901</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5448</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>701520</v>
+        <v>701148</v>
       </c>
       <c r="R2" t="n">
-        <v>7154839</v>
+        <v>7155247</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119719051</v>
+        <v>119719058</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>701248</v>
+        <v>701147</v>
       </c>
       <c r="R3" t="n">
-        <v>7155175</v>
+        <v>7155226</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119719060</v>
+        <v>119719059</v>
       </c>
       <c r="B4" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>701264</v>
+        <v>701141</v>
       </c>
       <c r="R4" t="n">
-        <v>7155153</v>
+        <v>7155241</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119719050</v>
+        <v>119719060</v>
       </c>
       <c r="B5" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>701225</v>
+        <v>701264</v>
       </c>
       <c r="R5" t="n">
-        <v>7155202</v>
+        <v>7155153</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,19 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119719055</v>
+        <v>119719049</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>701650</v>
+        <v>701148</v>
       </c>
       <c r="R6" t="n">
-        <v>7154795</v>
+        <v>7155258</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119719040</v>
+        <v>119719050</v>
       </c>
       <c r="B7" t="n">
-        <v>91870</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>701361</v>
+        <v>701225</v>
       </c>
       <c r="R7" t="n">
-        <v>7155081</v>
+        <v>7155202</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119719038</v>
+        <v>119719051</v>
       </c>
       <c r="B8" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>701148</v>
+        <v>701248</v>
       </c>
       <c r="R8" t="n">
-        <v>7155247</v>
+        <v>7155175</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119719059</v>
+        <v>119719052</v>
       </c>
       <c r="B9" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701141</v>
+        <v>701306</v>
       </c>
       <c r="R9" t="n">
-        <v>7155241</v>
+        <v>7155111</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119719048</v>
+        <v>119719053</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701693</v>
+        <v>701434</v>
       </c>
       <c r="R10" t="n">
-        <v>7154711</v>
+        <v>7155013</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,16 +1551,11 @@
         <v>119719054</v>
       </c>
       <c r="B11" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1695,19 +1645,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119719052</v>
+        <v>119719055</v>
       </c>
       <c r="B12" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1735,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701306</v>
+        <v>701650</v>
       </c>
       <c r="R12" t="n">
-        <v>7155111</v>
+        <v>7154795</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,12 +1745,7 @@
         <v>119719035</v>
       </c>
       <c r="B13" t="n">
-        <v>91862</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1899,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119719058</v>
+        <v>119719040</v>
       </c>
       <c r="B14" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>701147</v>
+        <v>701361</v>
       </c>
       <c r="R14" t="n">
-        <v>7155226</v>
+        <v>7155081</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,15 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119719049</v>
+        <v>119719030</v>
       </c>
       <c r="B15" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>701148</v>
+        <v>701166</v>
       </c>
       <c r="R15" t="n">
-        <v>7155258</v>
+        <v>7155254</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,37 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119719042</v>
+        <v>119719033</v>
       </c>
       <c r="B16" t="n">
-        <v>96891</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>5448</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>701561</v>
+        <v>701520</v>
       </c>
       <c r="R16" t="n">
-        <v>7154811</v>
+        <v>7154839</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,37 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119719030</v>
+        <v>119719048</v>
       </c>
       <c r="B17" t="n">
-        <v>90545</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>701166</v>
+        <v>701693</v>
       </c>
       <c r="R17" t="n">
-        <v>7155254</v>
+        <v>7154711</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,15 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119719053</v>
+        <v>119719042</v>
       </c>
       <c r="B18" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>701434</v>
+        <v>701561</v>
       </c>
       <c r="R18" t="n">
-        <v>7155013</v>
+        <v>7154811</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 32223-2024 artfynd.xlsx
+++ b/artfynd/A 32223-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719038</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719058</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719059</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719060</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719049</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719050</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719051</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719052</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719053</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719054</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719055</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719035</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719040</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719030</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719033</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719048</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,8 +2406,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719042</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>